--- a/recomendador/Tabla_Maestra_ZKTeco.xlsx
+++ b/recomendador/Tabla_Maestra_ZKTeco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TVCMTY-57298\Documents\recomendador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92037C7A-5B01-4DF7-A35D-642A74033D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B203C5-7C64-4E26-BD57-DB42F1DDFE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="704" activeTab="4" xr2:uid="{DB513028-4120-4D60-A8C2-889CF1E9B842}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="704" xr2:uid="{DB513028-4120-4D60-A8C2-889CF1E9B842}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3201" uniqueCount="278">
   <si>
     <t>ID</t>
   </si>
@@ -275,9 +275,6 @@
     <t>Índice de Protección</t>
   </si>
   <si>
-    <t>IP68</t>
-  </si>
-  <si>
     <t>ID (125 kHz)</t>
   </si>
   <si>
@@ -509,86 +506,383 @@
     <t>InBio</t>
   </si>
   <si>
-    <t>InBio160</t>
-  </si>
-  <si>
     <t>https://tvc.mx/products/16773</t>
   </si>
   <si>
     <t>ZKT368012</t>
   </si>
   <si>
-    <t>InBio460</t>
-  </si>
-  <si>
     <t>https://tvc.mx/products/5233</t>
   </si>
   <si>
-    <t>InBio260</t>
-  </si>
-  <si>
     <t>https://tvc.mx/products/3797</t>
   </si>
   <si>
-    <t>Lector RS485 como FR1200 o FR1500.
+    <t>ZKT0810058</t>
+  </si>
+  <si>
+    <t>Horus TL1 Pro</t>
+  </si>
+  <si>
+    <t>Horus</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/46090</t>
+  </si>
+  <si>
+    <t>ZKT0810023</t>
+  </si>
+  <si>
+    <t>Chip celular</t>
+  </si>
+  <si>
+    <t>4,300 mAh</t>
+  </si>
+  <si>
+    <t>8 horas</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/34671</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MA300</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/2485</t>
+  </si>
+  <si>
+    <t>ZKT0680051</t>
+  </si>
+  <si>
+    <t>MA300 AC 35</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/65995</t>
+  </si>
+  <si>
+    <t>ZKT061002</t>
+  </si>
+  <si>
+    <t>MA500</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/4432</t>
+  </si>
+  <si>
+    <t>ZKT0680042</t>
+  </si>
+  <si>
+    <t>LF10</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/32453</t>
+  </si>
+  <si>
+    <t>TF1700</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/2955</t>
+  </si>
+  <si>
+    <t>ZKT0810083</t>
+  </si>
+  <si>
+    <t>SpeedFace-V3L(Lite)</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/61402</t>
+  </si>
+  <si>
+    <t>ZKT0810074</t>
+  </si>
+  <si>
+    <t>SpeedFace-V5L[QR]</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/56433</t>
+  </si>
+  <si>
+    <t>ZKT0810069</t>
+  </si>
+  <si>
+    <t>SpeedFace-V3L</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/53368</t>
+  </si>
+  <si>
+    <t>ZKT0650026</t>
+  </si>
+  <si>
+    <t>FaceDepot-7BL</t>
+  </si>
+  <si>
+    <t>FaceDepot</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/28042</t>
+  </si>
+  <si>
+    <t>ZKT0680049</t>
+  </si>
+  <si>
+    <t>ProMA</t>
+  </si>
+  <si>
+    <t>IP66 &amp; IK07</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/53563</t>
+  </si>
+  <si>
+    <t>ZKT0810070</t>
+  </si>
+  <si>
+    <t>ProMA-QR</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/53568</t>
+  </si>
+  <si>
+    <t>ZKT0800031</t>
+  </si>
+  <si>
+    <t>S922</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>7,600 mAh</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/41232</t>
+  </si>
+  <si>
+    <t>4 ~ 12 horas</t>
+  </si>
+  <si>
+    <t>ZKT0810028</t>
+  </si>
+  <si>
+    <t>MiniAC Plus</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/35182</t>
+  </si>
+  <si>
+    <t>ZKT0650025</t>
+  </si>
+  <si>
+    <t>SpeedFace-H5L</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/28034</t>
+  </si>
+  <si>
+    <t>ZKT0810026</t>
+  </si>
+  <si>
+    <t>SpeedFace-V4L</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/35174</t>
+  </si>
+  <si>
+    <t>ZKT0810006</t>
+  </si>
+  <si>
+    <t>Elite Pass</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>IP68 &amp; IK04</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/32075</t>
+  </si>
+  <si>
+    <t>ZKT0720025</t>
+  </si>
+  <si>
+    <t>InBioPC-800</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/75840</t>
+  </si>
+  <si>
+    <t>ZKT0720023</t>
+  </si>
+  <si>
+    <t>C3-100 Plus</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/71205</t>
+  </si>
+  <si>
+    <t>Incluye Gabinete</t>
+  </si>
+  <si>
+    <t>Clave sin gabinete</t>
+  </si>
+  <si>
+    <t>Enlace sin gabinete</t>
+  </si>
+  <si>
+    <t>ZTA065008</t>
+  </si>
+  <si>
+    <t>InBio160B</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/19897</t>
+  </si>
+  <si>
+    <t>ZTA065009</t>
+  </si>
+  <si>
+    <t>InBio260B</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/19901</t>
+  </si>
+  <si>
+    <t>ZTA065010</t>
+  </si>
+  <si>
+    <t>InBio460B</t>
+  </si>
+  <si>
+    <t>ZKT0720022</t>
+  </si>
+  <si>
+    <t>C3-200 Plus</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/71200</t>
+  </si>
+  <si>
+    <t>ZKT0720024</t>
+  </si>
+  <si>
+    <t>C3-400 Plus</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/71210</t>
+  </si>
+  <si>
+    <t>ZKT065009</t>
+  </si>
+  <si>
+    <t>InBio160 Pro</t>
+  </si>
+  <si>
+    <t>InBio Pro</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/9641</t>
+  </si>
+  <si>
+    <t>ZKT065007</t>
+  </si>
+  <si>
+    <t>InBio260 Pro</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/8131</t>
+  </si>
+  <si>
+    <t>ZKT065006</t>
+  </si>
+  <si>
+    <t>InBio460 Pro</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/7809</t>
+  </si>
+  <si>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>Lector RS485 como QR500; 
 Lector Wiegand como KR500 o alguna UHF.</t>
   </si>
   <si>
-    <t>ZKT0810058</t>
-  </si>
-  <si>
-    <t>Horus TL1 Pro</t>
-  </si>
-  <si>
-    <t>Horus</t>
-  </si>
-  <si>
-    <t>https://tvc.mx/products/46090</t>
-  </si>
-  <si>
-    <t>ZKT0810023</t>
-  </si>
-  <si>
-    <t>HORUS-E1</t>
-  </si>
-  <si>
-    <t>Chip celular</t>
-  </si>
-  <si>
-    <t>4,300 mAh</t>
-  </si>
-  <si>
-    <t>8 horas</t>
-  </si>
-  <si>
-    <t>https://tvc.mx/products/34671</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>MA300</t>
-  </si>
-  <si>
-    <t>https://tvc.mx/products/2485</t>
-  </si>
-  <si>
-    <t>ZKT0680051</t>
-  </si>
-  <si>
-    <t>MA300 AC 35</t>
-  </si>
-  <si>
-    <t>https://tvc.mx/products/65995</t>
-  </si>
-  <si>
-    <t>ZKT061002</t>
-  </si>
-  <si>
-    <t>MA500</t>
-  </si>
-  <si>
-    <t>https://tvc.mx/products/4432</t>
+    <t>Lector RS485 como FR1200, FR1500 o QR500; 
+Lector Wiegand como KR500 o alguna UHF.</t>
+  </si>
+  <si>
+    <t>Lector RS485 como FR1200, FR1500; 
+Lector Wiegand como KR500, QR500 o alguna UHF.</t>
+  </si>
+  <si>
+    <t>Clave alterna con gabinete</t>
+  </si>
+  <si>
+    <t>Enlace alterno con gabinete</t>
+  </si>
+  <si>
+    <t>ZKT0650022</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/24733</t>
+  </si>
+  <si>
+    <t>ZTA065014</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/20920</t>
+  </si>
+  <si>
+    <t>En línea</t>
+  </si>
+  <si>
+    <t>Nuevo</t>
+  </si>
+  <si>
+    <t>Outlet</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/19905</t>
+  </si>
+  <si>
+    <t>Horus-E1</t>
+  </si>
+  <si>
+    <t>ZKT0720004</t>
+  </si>
+  <si>
+    <t>C2-260B</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/35523</t>
+  </si>
+  <si>
+    <t>Módulo DE-10 por PoE; 
+Lector RS485 como FR1200 o FR1500; 
+Lector Wiegand como KR500 o alguna UHF.</t>
+  </si>
+  <si>
+    <t>Módulo DM-10 por RS485; 
+Lector RS485 como FR1200 o FR1500 (solo RFID); 
+Lector Wiegand como KR500 o alguna UHF por medio de WR485.</t>
   </si>
 </sst>
 </file>
@@ -978,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ADD60D-2C97-426D-9463-37EADD9F0616}">
-  <dimension ref="A1:V1048576"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -987,12 +1281,17 @@
     <col min="11" max="14" width="11.5546875" style="5"/>
     <col min="15" max="15" width="18.5546875" style="5" customWidth="1"/>
     <col min="16" max="17" width="11.5546875" style="5"/>
-    <col min="18" max="18" width="17.44140625" customWidth="1"/>
-    <col min="19" max="20" width="18.44140625" customWidth="1"/>
-    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" customWidth="1"/>
+    <col min="20" max="21" width="17.44140625" customWidth="1"/>
+    <col min="22" max="22" width="23" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="17.44140625" customWidth="1"/>
+    <col min="25" max="26" width="18.44140625" customWidth="1"/>
+    <col min="27" max="27" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1042,25 +1341,43 @@
         <v>11</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R1" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Z1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1089,7 +1406,7 @@
         <v>2000</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1">
         <v>2000</v>
@@ -1112,23 +1429,29 @@
       <c r="Q2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -1157,7 +1480,7 @@
         <v>10000</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K3" s="1">
         <v>10000</v>
@@ -1180,23 +1503,29 @@
       <c r="Q3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U3" t="s">
-        <v>21</v>
-      </c>
-      <c r="V3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
@@ -1225,7 +1554,7 @@
         <v>50000</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K4" s="1">
         <v>50000</v>
@@ -1240,7 +1569,7 @@
         <v>20</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>21</v>
@@ -1248,34 +1577,40 @@
       <c r="Q4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U4" t="s">
-        <v>21</v>
-      </c>
-      <c r="V4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="E5" s="1">
         <v>50000</v>
@@ -1293,7 +1628,7 @@
         <v>50000</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K5" s="1">
         <v>50000</v>
@@ -1308,7 +1643,7 @@
         <v>20</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>21</v>
@@ -1316,34 +1651,40 @@
       <c r="Q5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U5" t="s">
-        <v>21</v>
-      </c>
-      <c r="V5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="1">
         <v>8000</v>
@@ -1361,7 +1702,7 @@
         <v>8000</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K6" s="1">
         <v>8000</v>
@@ -1376,7 +1717,7 @@
         <v>20</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>21</v>
@@ -1384,34 +1725,40 @@
       <c r="Q6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U6" t="s">
-        <v>21</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="R6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
         <v>6000</v>
@@ -1429,7 +1776,7 @@
         <v>6000</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K7" s="1">
         <v>6000</v>
@@ -1444,7 +1791,7 @@
         <v>20</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>21</v>
@@ -1452,34 +1799,40 @@
       <c r="Q7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U7" t="s">
-        <v>21</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="R7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
         <v>3000</v>
@@ -1497,7 +1850,7 @@
         <v>3000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K8" s="1">
         <v>3000</v>
@@ -1520,34 +1873,40 @@
       <c r="Q8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U8" t="s">
-        <v>21</v>
-      </c>
-      <c r="V8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1">
         <v>1000</v>
@@ -1565,7 +1924,7 @@
         <v>1000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K9" s="1">
         <v>1000</v>
@@ -1588,34 +1947,40 @@
       <c r="Q9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="T9" s="1" t="s">
+      <c r="R9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="U9" t="s">
-        <v>21</v>
-      </c>
-      <c r="V9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Z9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1">
         <v>3000</v>
@@ -1633,7 +1998,7 @@
         <v>3000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K10" s="1">
         <v>3000</v>
@@ -1656,34 +2021,40 @@
       <c r="Q10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U10" t="s">
-        <v>21</v>
-      </c>
-      <c r="V10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1">
         <v>500</v>
@@ -1701,7 +2072,7 @@
         <v>500</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K11" s="1">
         <v>500</v>
@@ -1724,34 +2095,40 @@
       <c r="Q11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U11" t="s">
-        <v>21</v>
-      </c>
-      <c r="V11" t="s">
+      <c r="R11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="E12" s="1">
         <v>500</v>
@@ -1769,7 +2146,7 @@
         <v>500</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K12" s="1">
         <v>500</v>
@@ -1792,34 +2169,40 @@
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U12" t="s">
-        <v>21</v>
-      </c>
-      <c r="V12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" s="1">
         <v>3000</v>
@@ -1837,7 +2220,7 @@
         <v>3000</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K13" s="1">
         <v>3000</v>
@@ -1860,34 +2243,40 @@
       <c r="Q13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="T13" s="1" t="s">
+      <c r="R13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y13" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="U13" t="s">
-        <v>21</v>
-      </c>
-      <c r="V13" t="s">
+      <c r="Z13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14" s="1">
         <v>1000</v>
@@ -1905,7 +2294,7 @@
         <v>1000</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K14" s="1">
         <v>1000</v>
@@ -1928,31 +2317,37 @@
       <c r="Q14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U14" t="s">
-        <v>21</v>
-      </c>
-      <c r="V14" t="s">
+      <c r="R14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>14</v>
@@ -1973,7 +2368,7 @@
         <v>500</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K15" s="5">
         <v>500</v>
@@ -1996,34 +2391,40 @@
       <c r="Q15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U15" t="s">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s">
+      <c r="R15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>124</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="E16" s="1">
         <v>500</v>
@@ -2064,34 +2465,40 @@
       <c r="Q16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U16" t="s">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s">
+      <c r="R16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="E17" s="5">
         <v>20000</v>
@@ -2109,7 +2516,7 @@
         <v>20000</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K17" s="5">
         <v>20000</v>
@@ -2132,34 +2539,40 @@
       <c r="Q17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U17" t="s">
-        <v>21</v>
-      </c>
-      <c r="V17" t="s">
+      <c r="R17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="E18" s="5">
         <v>3000</v>
@@ -2177,7 +2590,7 @@
         <v>3000</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K18" s="5">
         <v>3000</v>
@@ -2200,34 +2613,40 @@
       <c r="Q18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U18" t="s">
-        <v>21</v>
-      </c>
-      <c r="V18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="E19" s="5">
         <v>5000</v>
@@ -2245,7 +2664,7 @@
         <v>5000</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K19" s="5">
         <v>5000</v>
@@ -2268,34 +2687,40 @@
       <c r="Q19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U19" t="s">
-        <v>21</v>
-      </c>
-      <c r="V19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20" s="5">
         <v>5000</v>
@@ -2313,7 +2738,7 @@
         <v>5000</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K20" s="5">
         <v>5000</v>
@@ -2336,34 +2761,40 @@
       <c r="Q20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U20" t="s">
-        <v>21</v>
-      </c>
-      <c r="V20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E21" s="5">
         <v>3000</v>
@@ -2381,7 +2812,7 @@
         <v>3000</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K21" s="5">
         <v>3000</v>
@@ -2396,7 +2827,7 @@
         <v>20</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>20</v>
@@ -2404,34 +2835,40 @@
       <c r="Q21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U21" t="s">
-        <v>21</v>
-      </c>
-      <c r="V21" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22" s="5">
         <v>10000</v>
@@ -2449,7 +2886,7 @@
         <v>10000</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K22" s="5">
         <v>10000</v>
@@ -2464,7 +2901,7 @@
         <v>20</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>20</v>
@@ -2472,34 +2909,40 @@
       <c r="Q22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U22" t="s">
-        <v>21</v>
-      </c>
-      <c r="V22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E23" s="5">
         <v>30000</v>
@@ -2541,33 +2984,45 @@
         <v>21</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U23" t="s">
-        <v>21</v>
-      </c>
-      <c r="V23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="T23" t="s">
+        <v>154</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>236</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E24" s="5">
         <v>30000</v>
@@ -2609,33 +3064,47 @@
         <v>21</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="V24" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A25">
+        <v>17</v>
+      </c>
+      <c r="S24" s="7">
         <v>74162</v>
+      </c>
+      <c r="T24" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" s="5">
         <v>30000</v>
@@ -2677,33 +3146,45 @@
         <v>21</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="V25" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="T25" t="s">
+        <v>156</v>
+      </c>
+      <c r="U25" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E26" s="5">
         <v>800</v>
@@ -2744,34 +3225,44 @@
       <c r="Q26" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="V26" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>168</v>
+        <v>271</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E27" s="5">
         <v>6000</v>
@@ -2812,23 +3303,33 @@
       <c r="Q27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="U27" s="7" t="s">
+      <c r="R27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="V27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="AB27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>75019</v>
       </c>
@@ -2836,10 +3337,10 @@
         <v>12</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E28" s="5">
         <v>10000</v>
@@ -2857,7 +3358,7 @@
         <v>10000</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>23</v>
@@ -2872,7 +3373,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>21</v>
@@ -2880,34 +3381,44 @@
       <c r="Q28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="V28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E29" s="5">
         <v>10000</v>
@@ -2925,7 +3436,7 @@
         <v>10000</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>23</v>
@@ -2940,7 +3451,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>21</v>
@@ -2948,34 +3459,44 @@
       <c r="Q29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="R29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
       <c r="U29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="V29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E30" s="5">
         <v>30000</v>
@@ -2993,7 +3514,7 @@
         <v>30000</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K30" s="5">
         <v>30000</v>
@@ -3008,7 +3529,7 @@
         <v>20</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>21</v>
@@ -3016,57 +3537,1657 @@
       <c r="Q30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="V30" t="s">
+      <c r="R30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="5">
+        <v>5000</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="5">
+        <v>5000</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" s="5">
+        <v>5000</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="5">
+        <v>80000</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>74095</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="U31" s="7"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="U32" s="7"/>
-    </row>
-    <row r="33" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U33" s="7"/>
-    </row>
-    <row r="34" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U34" s="7"/>
-    </row>
-    <row r="35" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U35" s="7"/>
-    </row>
-    <row r="36" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U36" s="7"/>
-    </row>
-    <row r="37" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U37" s="7"/>
-    </row>
-    <row r="38" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U38" s="7"/>
-    </row>
-    <row r="39" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U39" s="7"/>
-    </row>
-    <row r="40" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U40" s="7"/>
-    </row>
-    <row r="41" spans="21:21" x14ac:dyDescent="0.3">
-      <c r="U41" s="7"/>
-    </row>
-    <row r="1048576" spans="18:18" x14ac:dyDescent="0.3">
-      <c r="R1048576" s="1"/>
+      <c r="E32" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="5">
+        <v>10000</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K32" s="5">
+        <v>10000</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="5">
+        <v>30000</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="5">
+        <v>3000</v>
+      </c>
+      <c r="F33" s="5">
+        <v>500</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="5">
+        <v>3000</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="5">
+        <v>3000</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F34" s="5">
+        <v>6000</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="5">
+        <v>10000</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K34" s="5">
+        <v>10000</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="5">
+        <v>3000</v>
+      </c>
+      <c r="F35" s="5">
+        <v>500</v>
+      </c>
+      <c r="G35" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="5">
+        <v>3000</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F36" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="5">
+        <v>10000</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA36" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E37" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F37" s="5">
+        <v>30000</v>
+      </c>
+      <c r="G37" s="5">
+        <v>10000</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="5">
+        <v>50000</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K37" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" s="5">
+        <v>500000</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F38" s="5">
+        <v>30000</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="5">
+        <v>50000</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="5">
+        <v>500000</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39" s="5">
+        <v>30000</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="5">
+        <v>30000</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" s="5">
+        <v>3000</v>
+      </c>
+      <c r="F40" s="5">
+        <v>3000</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="5">
+        <v>3000</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="5">
+        <v>3000</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" s="5">
+        <v>150000</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F41" s="5">
+        <v>6000</v>
+      </c>
+      <c r="G41" s="5">
+        <v>6000</v>
+      </c>
+      <c r="H41" s="5">
+        <v>3000</v>
+      </c>
+      <c r="I41" s="5">
+        <v>3000</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" s="5">
+        <v>6000</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="5">
+        <v>800</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="5">
+        <v>800</v>
+      </c>
+      <c r="I42" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K42" s="5">
+        <v>1000</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="5">
+        <v>150000</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E43" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F43" s="5">
+        <v>30000</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="5">
+        <v>4000</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="5">
+        <v>40000</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" s="5">
+        <v>40000</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E45" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K45" s="5">
+        <v>100000</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="5">
+        <v>500000</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E46" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="5">
+        <v>100000</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="5">
+        <v>500000</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="U46" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA46" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E47" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="5">
+        <v>100000</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="5">
+        <v>500000</v>
+      </c>
+      <c r="N47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="U47" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="5">
+        <v>60000</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="5">
+        <v>20000</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="5">
+        <v>60000</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="5">
+        <v>60000</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="5">
+        <v>100000</v>
+      </c>
+      <c r="N48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U48" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E49" s="5">
+        <v>60000</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="5">
+        <v>20000</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="5">
+        <v>60000</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" s="5">
+        <v>60000</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="5">
+        <v>100000</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V49" t="s">
+        <v>263</v>
+      </c>
+      <c r="W49" t="s">
+        <v>264</v>
+      </c>
+      <c r="X49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA49" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E50" s="5">
+        <v>60000</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="5">
+        <v>20000</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="5">
+        <v>60000</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" s="5">
+        <v>60000</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="5">
+        <v>100000</v>
+      </c>
+      <c r="N50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="V50" t="s">
+        <v>265</v>
+      </c>
+      <c r="W50" t="s">
+        <v>266</v>
+      </c>
+      <c r="X50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E51" s="5">
+        <v>30000</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="5">
+        <v>30000</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="5">
+        <v>200000</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="X51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>275</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3077,7 +5198,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD560C2-BF1C-4DA5-BB4B-058D0BDCFFDC}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.21875" customWidth="1"/>
@@ -3097,7 +5218,7 @@
         <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>28</v>
@@ -3127,7 +5248,7 @@
         <v>36</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -3246,7 +5367,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -3284,7 +5405,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>20</v>
@@ -3322,7 +5443,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>20</v>
@@ -3360,7 +5481,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -3398,7 +5519,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -3436,7 +5557,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
@@ -3474,7 +5595,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -3512,7 +5633,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
@@ -3550,7 +5671,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>20</v>
@@ -3588,7 +5709,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>20</v>
@@ -3626,7 +5747,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -3664,7 +5785,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
@@ -3702,7 +5823,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -3740,7 +5861,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
@@ -3778,7 +5899,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -3816,7 +5937,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
@@ -3854,7 +5975,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -3892,7 +6013,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
@@ -3930,96 +6051,96 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="1">
         <v>4</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>74162</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="1">
-        <v>2</v>
-      </c>
       <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,12 +6169,12 @@
         <v>20</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>162</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -4091,7 +6212,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>21</v>
@@ -4135,7 +6256,7 @@
         <v>20</v>
       </c>
       <c r="C28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>20</v>
@@ -4167,13 +6288,13 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>20</v>
@@ -4205,40 +6326,862 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>74095</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1">
+        <v>8</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="1">
         <v>2</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>21</v>
+      <c r="D46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1">
+        <v>4</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="1">
+        <v>8</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -4249,7 +7192,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D188FE-0A5F-4722-9988-1447CAAEAEC2}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -4351,7 +7294,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -4374,7 +7317,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
@@ -4397,7 +7340,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -4420,7 +7363,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>20</v>
@@ -4443,7 +7386,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -4466,7 +7409,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -4489,7 +7432,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>21</v>
@@ -4512,7 +7455,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>21</v>
@@ -4535,7 +7478,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -4558,7 +7501,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -4581,7 +7524,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -4604,7 +7547,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>21</v>
@@ -4627,7 +7570,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -4650,7 +7593,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>20</v>
@@ -4673,7 +7616,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -4696,7 +7639,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>20</v>
@@ -4719,7 +7662,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -4742,13 +7685,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>23</v>
@@ -4765,7 +7708,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>21</v>
@@ -4787,8 +7730,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>153</v>
+      <c r="A24" t="s">
+        <v>236</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>21</v>
@@ -4810,8 +7753,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>74162</v>
+      <c r="A25" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>21</v>
@@ -4834,7 +7777,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>20</v>
@@ -4857,7 +7800,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -4903,7 +7846,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
@@ -4926,7 +7869,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>21</v>
@@ -4945,6 +7888,489 @@
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>74095</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5122,7 +8548,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD578E9-46E5-410E-B6CF-C9D9B5BCC9DE}">
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.109375" customWidth="1"/>
@@ -5505,7 +8931,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>50</v>
@@ -5525,7 +8951,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>53</v>
@@ -5545,7 +8971,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>55</v>
@@ -5565,7 +8991,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>58</v>
@@ -5585,7 +9011,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>59</v>
@@ -5605,7 +9031,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>61</v>
@@ -5625,7 +9051,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>64</v>
@@ -5645,7 +9071,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>50</v>
@@ -5665,7 +9091,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>53</v>
@@ -5685,7 +9111,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>55</v>
@@ -5705,7 +9131,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>58</v>
@@ -5725,7 +9151,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>59</v>
@@ -5745,7 +9171,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>61</v>
@@ -5765,7 +9191,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>64</v>
@@ -5785,7 +9211,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>50</v>
@@ -5805,7 +9231,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>53</v>
@@ -5825,7 +9251,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>55</v>
@@ -5845,7 +9271,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>58</v>
@@ -5865,7 +9291,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>59</v>
@@ -5885,7 +9311,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>61</v>
@@ -5905,7 +9331,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>64</v>
@@ -5925,7 +9351,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>50</v>
@@ -5945,7 +9371,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>53</v>
@@ -5965,7 +9391,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>55</v>
@@ -5985,7 +9411,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>58</v>
@@ -6005,7 +9431,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>59</v>
@@ -6025,7 +9451,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>61</v>
@@ -6045,7 +9471,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>64</v>
@@ -6065,7 +9491,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>50</v>
@@ -6085,7 +9511,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>53</v>
@@ -6105,7 +9531,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>55</v>
@@ -6125,7 +9551,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>59</v>
@@ -6145,7 +9571,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>64</v>
@@ -6170,7 +9596,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>50</v>
@@ -6195,7 +9621,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>53</v>
@@ -6220,7 +9646,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>55</v>
@@ -6245,7 +9671,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>59</v>
@@ -6270,7 +9696,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>64</v>
@@ -6295,7 +9721,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>53</v>
@@ -6320,7 +9746,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>62</v>
@@ -6345,7 +9771,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>53</v>
@@ -6365,7 +9791,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>62</v>
@@ -6385,7 +9811,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>50</v>
@@ -6405,7 +9831,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>53</v>
@@ -6425,7 +9851,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>55</v>
@@ -6445,7 +9871,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>59</v>
@@ -6465,7 +9891,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>50</v>
@@ -6485,7 +9911,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>53</v>
@@ -6505,7 +9931,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>55</v>
@@ -6525,7 +9951,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>59</v>
@@ -6545,7 +9971,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>50</v>
@@ -6565,7 +9991,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>53</v>
@@ -6585,7 +10011,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>55</v>
@@ -6605,7 +10031,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>59</v>
@@ -6625,7 +10051,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>50</v>
@@ -6645,7 +10071,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>53</v>
@@ -6665,7 +10091,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>55</v>
@@ -6685,7 +10111,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>59</v>
@@ -6705,7 +10131,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>50</v>
@@ -6725,7 +10151,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>53</v>
@@ -6745,7 +10171,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>55</v>
@@ -6765,7 +10191,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>59</v>
@@ -6785,7 +10211,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>50</v>
@@ -6805,7 +10231,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>53</v>
@@ -6825,7 +10251,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>55</v>
@@ -6845,7 +10271,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>58</v>
@@ -6865,7 +10291,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>59</v>
@@ -6885,7 +10311,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>61</v>
@@ -6905,7 +10331,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>50</v>
@@ -6925,7 +10351,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>53</v>
@@ -6945,7 +10371,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>55</v>
@@ -6965,7 +10391,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>58</v>
@@ -6985,7 +10411,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>59</v>
@@ -7005,7 +10431,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>61</v>
@@ -7025,7 +10451,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>50</v>
@@ -7045,7 +10471,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>53</v>
@@ -7065,7 +10491,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>55</v>
@@ -7085,7 +10511,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>58</v>
@@ -7105,7 +10531,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>59</v>
@@ -7125,7 +10551,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>61</v>
@@ -7145,7 +10571,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>62</v>
@@ -7165,7 +10591,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>64</v>
@@ -7185,7 +10611,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>50</v>
@@ -7205,7 +10631,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>53</v>
@@ -7225,7 +10651,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>55</v>
@@ -7245,7 +10671,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>58</v>
@@ -7265,7 +10691,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>59</v>
@@ -7285,7 +10711,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>61</v>
@@ -7305,7 +10731,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>58</v>
@@ -7325,7 +10751,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>61</v>
@@ -7344,8 +10770,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="4" t="s">
-        <v>153</v>
+      <c r="A108" t="s">
+        <v>236</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>58</v>
@@ -7364,8 +10790,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="4" t="s">
-        <v>153</v>
+      <c r="A109" t="s">
+        <v>236</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>61</v>
@@ -7384,8 +10810,8 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>74162</v>
+      <c r="A110" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>58</v>
@@ -7404,8 +10830,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>74162</v>
+      <c r="A111" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>61</v>
@@ -7425,7 +10851,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>50</v>
@@ -7445,7 +10871,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>53</v>
@@ -7465,7 +10891,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>55</v>
@@ -7485,7 +10911,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>59</v>
@@ -7505,7 +10931,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>50</v>
@@ -7525,7 +10951,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>53</v>
@@ -7545,7 +10971,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>55</v>
@@ -7565,7 +10991,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>59</v>
@@ -7625,7 +11051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>58</v>
@@ -7645,7 +11071,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>61</v>
@@ -7664,25 +11090,1644 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
+      <c r="A124" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
+      <c r="A126" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
+      <c r="A127" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/recomendador/Tabla_Maestra_ZKTeco.xlsx
+++ b/recomendador/Tabla_Maestra_ZKTeco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TVCMTY-57298\Documents\recomendador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B203C5-7C64-4E26-BD57-DB42F1DDFE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222444EE-EB6D-484E-B502-BA2B6D796D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="704" xr2:uid="{DB513028-4120-4D60-A8C2-889CF1E9B842}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="704" activeTab="4" xr2:uid="{DB513028-4120-4D60-A8C2-889CF1E9B842}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3201" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3301" uniqueCount="287">
   <si>
     <t>ID</t>
   </si>
@@ -883,6 +883,33 @@
     <t>Módulo DM-10 por RS485; 
 Lector RS485 como FR1200 o FR1500 (solo RFID); 
 Lector Wiegand como KR500 o alguna UHF por medio de WR485.</t>
+  </si>
+  <si>
+    <t>ZKT0810089</t>
+  </si>
+  <si>
+    <t>Horus H1</t>
+  </si>
+  <si>
+    <t>5,200 mAh</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/75230</t>
+  </si>
+  <si>
+    <t>5 horas</t>
+  </si>
+  <si>
+    <t>ZKT1140003</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/88760</t>
   </si>
 </sst>
 </file>
@@ -932,7 +959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -957,6 +984,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1272,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ADD60D-2C97-426D-9463-37EADD9F0616}">
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -1283,7 +1313,8 @@
     <col min="16" max="17" width="11.5546875" style="5"/>
     <col min="18" max="18" width="15.109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="16.44140625" customWidth="1"/>
-    <col min="20" max="21" width="17.44140625" customWidth="1"/>
+    <col min="20" max="20" width="17.44140625" customWidth="1"/>
+    <col min="21" max="21" width="17.44140625" style="7" customWidth="1"/>
     <col min="22" max="22" width="23" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
     <col min="24" max="24" width="17.44140625" customWidth="1"/>
@@ -5189,6 +5220,154 @@
         <v>275</v>
       </c>
     </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M52" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U52" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y52" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z52" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="AA52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="5">
+        <v>500</v>
+      </c>
+      <c r="G53" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" s="5">
+        <v>1000</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="5">
+        <v>150000</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P53" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U53" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>286</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5198,10 +5377,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD560C2-BF1C-4DA5-BB4B-058D0BDCFFDC}">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" style="9" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" customWidth="1"/>
@@ -7184,6 +7363,82 @@
         <v>277</v>
       </c>
     </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7192,7 +7447,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D188FE-0A5F-4722-9988-1447CAAEAEC2}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -7625,7 +7880,7 @@
         <v>23</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>44</v>
@@ -7648,7 +7903,7 @@
         <v>23</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>44</v>
@@ -7671,7 +7926,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>44</v>
@@ -7694,7 +7949,7 @@
         <v>23</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>44</v>
@@ -8371,6 +8626,52 @@
       </c>
       <c r="G51" s="3" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -8548,7 +8849,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD578E9-46E5-410E-B6CF-C9D9B5BCC9DE}">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L209"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.109375" customWidth="1"/>
@@ -10574,39 +10875,39 @@
         <v>142</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -10614,7 +10915,7 @@
         <v>147</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>37</v>
@@ -10634,7 +10935,7 @@
         <v>147</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>37</v>
@@ -10643,7 +10944,7 @@
         <v>43</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>21</v>
@@ -10654,19 +10955,19 @@
         <v>147</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -10674,19 +10975,19 @@
         <v>147</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -10694,30 +10995,30 @@
         <v>147</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>44</v>
@@ -10734,7 +11035,7 @@
         <v>233</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>39</v>
@@ -10750,11 +11051,11 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="4" t="s">
-        <v>233</v>
+      <c r="A107" t="s">
+        <v>236</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>39</v>
@@ -10774,7 +11075,7 @@
         <v>236</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>39</v>
@@ -10790,11 +11091,11 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>236</v>
+      <c r="A109" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>39</v>
@@ -10814,7 +11115,7 @@
         <v>239</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>39</v>
@@ -10831,22 +11132,22 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -10854,7 +11155,7 @@
         <v>158</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>37</v>
@@ -10874,7 +11175,7 @@
         <v>158</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>37</v>
@@ -10883,7 +11184,7 @@
         <v>43</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>21</v>
@@ -10894,7 +11195,7 @@
         <v>158</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>37</v>
@@ -10911,10 +11212,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>37</v>
@@ -10923,7 +11224,7 @@
         <v>43</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>21</v>
@@ -10934,7 +11235,7 @@
         <v>162</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>37</v>
@@ -10954,7 +11255,7 @@
         <v>162</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>37</v>
@@ -10963,7 +11264,7 @@
         <v>43</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>21</v>
@@ -10974,7 +11275,7 @@
         <v>162</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>37</v>
@@ -10990,23 +11291,23 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="4" t="s">
-        <v>162</v>
+      <c r="A119">
+        <v>75019</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -11014,7 +11315,7 @@
         <v>75019</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>37</v>
@@ -11030,14 +11331,14 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <v>75019</v>
+      <c r="A121" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>44</v>
@@ -11054,7 +11355,7 @@
         <v>173</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>39</v>
@@ -11071,13 +11372,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>44</v>
@@ -11094,7 +11395,7 @@
         <v>176</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>37</v>
@@ -11111,22 +11412,22 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -11134,7 +11435,7 @@
         <v>183</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>37</v>
@@ -11154,7 +11455,7 @@
         <v>183</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>37</v>
@@ -11163,7 +11464,7 @@
         <v>43</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>21</v>
@@ -11174,19 +11475,19 @@
         <v>183</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -11194,19 +11495,19 @@
         <v>183</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -11214,39 +11515,39 @@
         <v>183</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -11254,7 +11555,7 @@
         <v>186</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>37</v>
@@ -11274,7 +11575,7 @@
         <v>186</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>37</v>
@@ -11283,7 +11584,7 @@
         <v>43</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>21</v>
@@ -11294,19 +11595,19 @@
         <v>186</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
@@ -11314,19 +11615,19 @@
         <v>186</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -11334,39 +11635,39 @@
         <v>186</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -11374,7 +11675,7 @@
         <v>189</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>37</v>
@@ -11394,7 +11695,7 @@
         <v>189</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>37</v>
@@ -11403,7 +11704,7 @@
         <v>43</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>21</v>
@@ -11414,19 +11715,19 @@
         <v>189</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -11434,19 +11735,19 @@
         <v>189</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -11454,39 +11755,39 @@
         <v>189</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -11494,7 +11795,7 @@
         <v>192</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>37</v>
@@ -11514,7 +11815,7 @@
         <v>192</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>37</v>
@@ -11523,7 +11824,7 @@
         <v>43</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>21</v>
@@ -11534,19 +11835,19 @@
         <v>192</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -11554,19 +11855,19 @@
         <v>192</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -11574,39 +11875,39 @@
         <v>192</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -11614,7 +11915,7 @@
         <v>196</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>37</v>
@@ -11634,7 +11935,7 @@
         <v>196</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>37</v>
@@ -11643,7 +11944,7 @@
         <v>43</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>21</v>
@@ -11654,19 +11955,19 @@
         <v>196</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -11674,19 +11975,19 @@
         <v>196</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -11694,39 +11995,39 @@
         <v>196</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -11734,7 +12035,7 @@
         <v>200</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>37</v>
@@ -11754,7 +12055,7 @@
         <v>200</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>37</v>
@@ -11763,7 +12064,7 @@
         <v>43</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>21</v>
@@ -11774,19 +12075,19 @@
         <v>200</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -11794,19 +12095,19 @@
         <v>200</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -11814,39 +12115,39 @@
         <v>200</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -11854,7 +12155,7 @@
         <v>203</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>37</v>
@@ -11874,7 +12175,7 @@
         <v>203</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>37</v>
@@ -11883,7 +12184,7 @@
         <v>43</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>21</v>
@@ -11894,7 +12195,7 @@
         <v>203</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>37</v>
@@ -11911,10 +12212,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>37</v>
@@ -11923,7 +12224,7 @@
         <v>43</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>21</v>
@@ -11934,7 +12235,7 @@
         <v>209</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>37</v>
@@ -11954,7 +12255,7 @@
         <v>209</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>37</v>
@@ -11963,7 +12264,7 @@
         <v>43</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>21</v>
@@ -11974,19 +12275,19 @@
         <v>209</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -11994,19 +12295,19 @@
         <v>209</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -12014,39 +12315,39 @@
         <v>209</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
@@ -12054,7 +12355,7 @@
         <v>212</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>37</v>
@@ -12074,7 +12375,7 @@
         <v>212</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>37</v>
@@ -12083,7 +12384,7 @@
         <v>43</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>21</v>
@@ -12094,19 +12395,19 @@
         <v>212</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
@@ -12114,19 +12415,19 @@
         <v>212</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -12134,39 +12435,39 @@
         <v>212</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -12174,7 +12475,7 @@
         <v>215</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>37</v>
@@ -12194,7 +12495,7 @@
         <v>215</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>37</v>
@@ -12203,7 +12504,7 @@
         <v>43</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>21</v>
@@ -12214,19 +12515,19 @@
         <v>215</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -12234,19 +12535,19 @@
         <v>215</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -12254,39 +12555,39 @@
         <v>215</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -12294,7 +12595,7 @@
         <v>218</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>37</v>
@@ -12314,7 +12615,7 @@
         <v>218</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>37</v>
@@ -12323,7 +12624,7 @@
         <v>43</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>21</v>
@@ -12334,19 +12635,19 @@
         <v>218</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -12354,19 +12655,19 @@
         <v>218</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -12374,27 +12675,27 @@
         <v>218</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>37</v>
@@ -12414,7 +12715,7 @@
         <v>223</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>37</v>
@@ -12431,10 +12732,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>37</v>
@@ -12454,7 +12755,7 @@
         <v>226</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>37</v>
@@ -12471,10 +12772,10 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>37</v>
@@ -12494,7 +12795,7 @@
         <v>241</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>37</v>
@@ -12511,10 +12812,10 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>37</v>
@@ -12534,7 +12835,7 @@
         <v>244</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>37</v>
@@ -12551,10 +12852,10 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>37</v>
@@ -12574,7 +12875,7 @@
         <v>247</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>37</v>
@@ -12591,10 +12892,10 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>37</v>
@@ -12614,7 +12915,7 @@
         <v>251</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>37</v>
@@ -12631,10 +12932,10 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>37</v>
@@ -12654,7 +12955,7 @@
         <v>254</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>37</v>
@@ -12671,10 +12972,10 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>37</v>
@@ -12694,7 +12995,7 @@
         <v>272</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>37</v>
@@ -12711,22 +13012,102 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/recomendador/Tabla_Maestra_ZKTeco.xlsx
+++ b/recomendador/Tabla_Maestra_ZKTeco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TVCMTY-57298\Documents\recomendador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222444EE-EB6D-484E-B502-BA2B6D796D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D907C1-DC66-4D6C-8676-599B23F1DB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="704" activeTab="4" xr2:uid="{DB513028-4120-4D60-A8C2-889CF1E9B842}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="704" activeTab="5" xr2:uid="{DB513028-4120-4D60-A8C2-889CF1E9B842}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,12 @@
     <sheet name="Comunicacion" sheetId="3" r:id="rId3"/>
     <sheet name="Software" sheetId="4" r:id="rId4"/>
     <sheet name="Compatibilidad" sheetId="5" r:id="rId5"/>
-    <sheet name="Listas" sheetId="6" r:id="rId6"/>
+    <sheet name="Licencias" sheetId="7" r:id="rId6"/>
+    <sheet name="Licencias_Software" sheetId="8" r:id="rId7"/>
+    <sheet name="Leyenda_Licencias" sheetId="9" r:id="rId8"/>
+    <sheet name="Listas" sheetId="6" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3301" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3765" uniqueCount="532">
   <si>
     <t>ID</t>
   </si>
@@ -910,6 +913,755 @@
   </si>
   <si>
     <t>https://tvc.mx/products/88760</t>
+  </si>
+  <si>
+    <t>Clave TVC</t>
+  </si>
+  <si>
+    <t>Licencia</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Vigencia</t>
+  </si>
+  <si>
+    <t>Capacidad</t>
+  </si>
+  <si>
+    <t>Checadores</t>
+  </si>
+  <si>
+    <t>Empleados</t>
+  </si>
+  <si>
+    <t>Puertas</t>
+  </si>
+  <si>
+    <t>Requiere</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>BioTime Pro Gratuita (incluida al instalar)</t>
+  </si>
+  <si>
+    <t>Gratuita</t>
+  </si>
+  <si>
+    <t>Vitalicia</t>
+  </si>
+  <si>
+    <t>2 Checadores, 200 Empleados, 1 App y 1 Multiempresa</t>
+  </si>
+  <si>
+    <t>Se activa automáticamente al instalar. Al activar una licencia base, la reemplaza (capacidades no acumulables).</t>
+  </si>
+  <si>
+    <t>ZKT0820003</t>
+  </si>
+  <si>
+    <t>BioTime Pro Starter</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>5 Checadores, 500 Empleados, 1 APP y 1 Multicompañía</t>
+  </si>
+  <si>
+    <t>ZKT0820002</t>
+  </si>
+  <si>
+    <t>BioTime Pro Lite</t>
+  </si>
+  <si>
+    <t>10 Checadores, 1000 Empleados, 1 APP y 1 Multicompañía</t>
+  </si>
+  <si>
+    <t>ZKT0820004</t>
+  </si>
+  <si>
+    <t>BioTime Pro Standard</t>
+  </si>
+  <si>
+    <t>20 Checadores, 2000 Empleados, 1 APP y 2 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820005</t>
+  </si>
+  <si>
+    <t>BioTime Pro Premium</t>
+  </si>
+  <si>
+    <t>50 Checadores, 6000 Empleados, 1 APP y 5 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820006</t>
+  </si>
+  <si>
+    <t>BioTime Pro Prime</t>
+  </si>
+  <si>
+    <t>75 Checadores, 8000 Empleados, 1 APP y 7 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820007</t>
+  </si>
+  <si>
+    <t>BioTime Pro Enterprise</t>
+  </si>
+  <si>
+    <t>100 Checadores, 12000 Empleados, 1 APP y 10 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820008</t>
+  </si>
+  <si>
+    <t>BioTime Pro Business</t>
+  </si>
+  <si>
+    <t>150 Checadores, 15000 Empleados, 1 APP y 15 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820009</t>
+  </si>
+  <si>
+    <t>BioTime Pro Professional</t>
+  </si>
+  <si>
+    <t>200 Checadores, 20000 Empleados, 1 APP y 20 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820010</t>
+  </si>
+  <si>
+    <t>BioTime Pro Big Project</t>
+  </si>
+  <si>
+    <t>300 Checadores, 30000 Empleados, 1 APP y 30 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820011</t>
+  </si>
+  <si>
+    <t>BioTime Pro Great Project</t>
+  </si>
+  <si>
+    <t>500 Checadores, 50000 Empleados, 1 APP y 50 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820012</t>
+  </si>
+  <si>
+    <t>BioTime Pro Ultimate</t>
+  </si>
+  <si>
+    <t>800 Checadores, 80000 Empleados, 1 APP y 50 Multicompañías</t>
+  </si>
+  <si>
+    <t>ZKT0820015</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Basic</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>20 APPs</t>
+  </si>
+  <si>
+    <t>Licencia base que soporte la cantidad de APPs móviles</t>
+  </si>
+  <si>
+    <t>ZKT0820016</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Lite</t>
+  </si>
+  <si>
+    <t>50 APPs</t>
+  </si>
+  <si>
+    <t>ZKT0820017</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Standard</t>
+  </si>
+  <si>
+    <t>100 APPs</t>
+  </si>
+  <si>
+    <t>ZKT0820018</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Professional</t>
+  </si>
+  <si>
+    <t>200 APPs</t>
+  </si>
+  <si>
+    <t>ZKT0820019</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Premium</t>
+  </si>
+  <si>
+    <t>300 APPs</t>
+  </si>
+  <si>
+    <t>ZKT0820020</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Enterprise</t>
+  </si>
+  <si>
+    <t>500 APPs</t>
+  </si>
+  <si>
+    <t>ZKT0820021</t>
+  </si>
+  <si>
+    <t>BioTime Pro App Business</t>
+  </si>
+  <si>
+    <t>800 APPs</t>
+  </si>
+  <si>
+    <t>ZKT0820014</t>
+  </si>
+  <si>
+    <t>BioTime Pro Additional User</t>
+  </si>
+  <si>
+    <t>Aumento</t>
+  </si>
+  <si>
+    <t>1 Empleado adicional</t>
+  </si>
+  <si>
+    <t>Licencia base</t>
+  </si>
+  <si>
+    <t>ZKT0820013</t>
+  </si>
+  <si>
+    <t>BioTime Pro Additional Devices</t>
+  </si>
+  <si>
+    <t>5 Checadores adicionales</t>
+  </si>
+  <si>
+    <t>ZKT0820026</t>
+  </si>
+  <si>
+    <t>BioTime Pro Additional Company</t>
+  </si>
+  <si>
+    <t>1 Compañía adicional</t>
+  </si>
+  <si>
+    <t>ZKT0820146</t>
+  </si>
+  <si>
+    <t>BioTime Cloud 2.0 Lite</t>
+  </si>
+  <si>
+    <t>Suscripción</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>3 Checadores, 25 Empleados, 10 APPs y 37500 Eventos</t>
+  </si>
+  <si>
+    <t>ZKT0820147</t>
+  </si>
+  <si>
+    <t>BioTime Cloud 2.0 Standard</t>
+  </si>
+  <si>
+    <t>6 Checadores, 50 Empleados, 25 APPs y 75000 Eventos</t>
+  </si>
+  <si>
+    <t>ZKT0820148</t>
+  </si>
+  <si>
+    <t>BioTime Cloud 2.0 Professional</t>
+  </si>
+  <si>
+    <t>15 Checadores, 100 Empleados, 75 APPs y 150000 Eventos</t>
+  </si>
+  <si>
+    <t>ZKT0820149</t>
+  </si>
+  <si>
+    <t>BioTime Cloud 2.0 Enterprise</t>
+  </si>
+  <si>
+    <t>40 Checadores, 300 Empleados, 300 APPs y 450000 Eventos</t>
+  </si>
+  <si>
+    <t>ZKT0820150</t>
+  </si>
+  <si>
+    <t>BioTime Cloud 2.0 Premium</t>
+  </si>
+  <si>
+    <t>60 Checadores, 500 Empleados, 500 APPs y 750000 Eventos</t>
+  </si>
+  <si>
+    <t>ZKT0740100</t>
+  </si>
+  <si>
+    <t>ZKCVA-FREE</t>
+  </si>
+  <si>
+    <t>Acceso/Asistencia</t>
+  </si>
+  <si>
+    <t>2000 Empleados, 15 Puertas de Acceso, 6 Checadores, 64 Canales de Video, 1 APP de Administrador y 5 APPs de Empleados</t>
+  </si>
+  <si>
+    <t>Sin costo al adquirir equipos compatibles (validar elegibilidad con el asesor). Existen licencias con costo hasta 25 puertas, 25 puntos de asistencia o 4,000 usuarios (consultar clave y costo con el asesor).</t>
+  </si>
+  <si>
+    <t>ZKT0740042</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P5</t>
+  </si>
+  <si>
+    <t>5 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>Incluye 30,000 empleados, 2,000 departamentos, 2,000 áreas, APIs activas, 1 App de administrador, 50 Apps de empleados y 64 canales de video (salvo indicación).</t>
+  </si>
+  <si>
+    <t>ZKT0740043</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P10</t>
+  </si>
+  <si>
+    <t>10 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740044</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P25</t>
+  </si>
+  <si>
+    <t>25 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740045</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P50</t>
+  </si>
+  <si>
+    <t>50 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740046</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P75</t>
+  </si>
+  <si>
+    <t>75 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740047</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P100</t>
+  </si>
+  <si>
+    <t>100 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740119</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P150</t>
+  </si>
+  <si>
+    <t>150 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740118</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P200</t>
+  </si>
+  <si>
+    <t>200 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740115</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-P250</t>
+  </si>
+  <si>
+    <t>250 Puertas de Acceso</t>
+  </si>
+  <si>
+    <t>ZKT0740049</t>
+  </si>
+  <si>
+    <t>ZKBioCV-AC-ADDON-P5</t>
+  </si>
+  <si>
+    <t>5 Puertas de Acceso Adicionales</t>
+  </si>
+  <si>
+    <t>Licencia base de 25 puertas o superior</t>
+  </si>
+  <si>
+    <t>ZKT0820112</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-P5</t>
+  </si>
+  <si>
+    <t>5 Checadores</t>
+  </si>
+  <si>
+    <t>ZKT0820113</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-P10</t>
+  </si>
+  <si>
+    <t>10 Checadores</t>
+  </si>
+  <si>
+    <t>ZKT0820114</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-P25</t>
+  </si>
+  <si>
+    <t>25 Checadores</t>
+  </si>
+  <si>
+    <t>ZKT0820115</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-P50</t>
+  </si>
+  <si>
+    <t>50 Checadores</t>
+  </si>
+  <si>
+    <t>ZKT0820116</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-P75</t>
+  </si>
+  <si>
+    <t>75 Checadores</t>
+  </si>
+  <si>
+    <t>ZKT0820117</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-P100</t>
+  </si>
+  <si>
+    <t>100 Checadores</t>
+  </si>
+  <si>
+    <t>ZKT0820118</t>
+  </si>
+  <si>
+    <t>ZKBioCV-TA-ADDON-P5</t>
+  </si>
+  <si>
+    <t>5 Checadores Adicionales</t>
+  </si>
+  <si>
+    <t>Licencia base de 25 checadores o superior</t>
+  </si>
+  <si>
+    <t>ZKBio Zlink (gratuito)</t>
+  </si>
+  <si>
+    <t>Software gratuito para equipos con protocolo BEST (sin clave TVC)</t>
+  </si>
+  <si>
+    <t>Compatible con equipos en protocolo BEST.</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Despliegue</t>
+  </si>
+  <si>
+    <t>Control de asistencia mediante protocolo PUSH con licenciamiento vitalicio.</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Incluye versión gratuita automática (2 checadores, 200 empleados, 1 App, 1 multiempresa); al activar una licencia base la reemplaza y las capacidades no son acumulables.
+Las licencias de aumento requieren licencia base y un proceso de unificación (copia de la licencia base activa); durante la unificación la licencia puede quedar temporalmente deshabilitada.
+No es posible unificar dos o más licencias base entre sí; para crecer se usan licencias de aumento.
+Migración de servidor o falla de hardware: reset de licencia gratuito (si no se detecta uso indebido).
+Procesar licencia, reset o unificación toma de 3 a 5 días hábiles. No se aceptan devoluciones.</t>
+  </si>
+  <si>
+    <t>Plataforma de control de asistencia en la nube (AWS) mediante protocolo PUSH, por suscripción anual.</t>
+  </si>
+  <si>
+    <t>Nube</t>
+  </si>
+  <si>
+    <t>No requiere instalación: se accede desde un navegador web. No hay proceso de reset de licencia.
+No se pueden combinar ni unificar suscripciones; tampoco ampliar terminales, empleados o apps de una suscripción (hay que adquirir una de mayor capacidad, que reemplaza la actual).
+La capacidad de eventos sí puede ampliarse de forma permanente con una actualización adicional.
+Activación de 3 a 5 días hábiles. No se aceptan devoluciones.</t>
+  </si>
+  <si>
+    <t>Software ligero WEB para pequeñas y medianas empresas, con licencia vitalicia base.</t>
+  </si>
+  <si>
+    <t>Local (Web)</t>
+  </si>
+  <si>
+    <t>La licencia gratuita se obtiene al adquirir equipos compatibles; validar elegibilidad con el asesor.
+Con costo existen licencias para ampliar hasta 25 puertas, 25 puntos de asistencia o 4,000 usuarios (consultar clave TVC y costo).
+Si el proyecto requiere más capacidad, evaluar ZKBio CVSecurity.
+Reset gratuito en migración o falla de hardware (si no hay uso indebido). 3 a 5 días hábiles. No se aceptan devoluciones.</t>
+  </si>
+  <si>
+    <t>Software modular para soluciones escalables y robustas, con licencias vitalicias cotizables por módulo.</t>
+  </si>
+  <si>
+    <t>Salvo indicación, las licencias base incluyen 30,000 empleados, 2,000 departamentos, 2,000 áreas, APIs activas, 1 App de administrador, 50 Apps de empleados y 64 canales de video.
+Aumentos de Acceso o Asistencia requieren unificación con la licencia base (copia de la licencia activa); la licencia puede quedar temporalmente deshabilitada durante el proceso.
+Se pueden unificar licencias de distintos módulos en una misma instalación, pero no dos o más bases del mismo módulo (Acceso, Asistencia, Visitas, Patrullaje y Hotel).
+Patrullaje requiere licencia activa en el Módulo de Acceso.
+Reset gratuito (si no hay uso indebido). 3 a 5 días hábiles. No se aceptan devoluciones.</t>
+  </si>
+  <si>
+    <t>Software gratuito para equipos con protocolo BEST.</t>
+  </si>
+  <si>
+    <t>Gratuito, sin clave TVC. Para equipos que trabajan con protocolo BEST.</t>
+  </si>
+  <si>
+    <t>Hoja</t>
+  </si>
+  <si>
+    <t>Qué contiene</t>
+  </si>
+  <si>
+    <t>Licencias</t>
+  </si>
+  <si>
+    <t>Una fila por licencia (clave TVC). Copia esta hoja a tu Tabla_Maestra_ZKTeco.xlsx con el mismo nombre y encabezados.</t>
+  </si>
+  <si>
+    <t>Licencias_Software</t>
+  </si>
+  <si>
+    <t>Una fila por software: descripción, despliegue y "puntos importantes" (una nota por renglón dentro de la celda).</t>
+  </si>
+  <si>
+    <t>Columna (Licencias)</t>
+  </si>
+  <si>
+    <t>Cómo llenarla</t>
+  </si>
+  <si>
+    <t>Clave del producto. Vacía si es gratuita o sin clave (ej. ZKBio Zlink, versión gratuita de BioTime Pro).</t>
+  </si>
+  <si>
+    <t>Nombre visible de la licencia.</t>
+  </si>
+  <si>
+    <t>Debe escribirse igual (o casi igual) que en la hoja "Software" de la tabla maestra: así se cruza con los equipos compatibles (ej. "BioTime Pro", "ZKBio CVSecurity").</t>
+  </si>
+  <si>
+    <t>Acceso, Asistencia, Visitas, etc. Si aplica a varios: "Acceso/Asistencia". Solo Acceso y Asistencia se cruzan por módulo con la hoja Compatibilidad; los demás módulos se cruzan por software.</t>
+  </si>
+  <si>
+    <t>Base, Aumento, App, Suscripción, Gratuita o Bajo proyecto.</t>
+  </si>
+  <si>
+    <t>Vitalicia, Anual, 36 meses, 1 año, Gratuita (o vacío si no se indica).</t>
+  </si>
+  <si>
+    <t>Texto libre con la capacidad tal como se presenta al cliente.</t>
+  </si>
+  <si>
+    <t>Checadores / Empleados / Puertas</t>
+  </si>
+  <si>
+    <t>Números (opcionales) usados por los filtros de capacidad mínima. Déjalos vacíos si no aplican.</t>
+  </si>
+  <si>
+    <t>Texto libre con requisitos (ej. "Licencia base de 25 puertas o superior").</t>
+  </si>
+  <si>
+    <t>Texto libre adicional.</t>
+  </si>
+  <si>
+    <t>Ilimitadas</t>
+  </si>
+  <si>
+    <t>APPs</t>
+  </si>
+  <si>
+    <t>Imagen</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49130</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/68070</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31258</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31298</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31262</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31318</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31306</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/70895</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/70890</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/70900</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/70905</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/70910</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31302</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31322</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/33486</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31330</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31286</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31282</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31270</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31326</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31310</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31274</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31254</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31266</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31278</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31290</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31294</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/31314</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49135</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49140</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49175</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49150</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49145</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/80492</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/80487</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/79550</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49160</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49180</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49190</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49205</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49200</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49210</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49195</t>
+  </si>
+  <si>
+    <t>https://tvc.mx/products/49185</t>
+  </si>
+  <si>
+    <t>img/licencias/BTPFREE.png</t>
+  </si>
+  <si>
+    <t>img/licencias/ZLINKFREE.png</t>
   </si>
 </sst>
 </file>
@@ -959,7 +1711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -988,6 +1740,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4655,7 +5412,7 @@
         <v>23</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q44" s="5" t="s">
         <v>20</v>
@@ -13117,6 +13874,1930 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4323FEF8-9A72-43CC-8BE6-9B44175C2B39}">
+  <dimension ref="A1:Q47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="108" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="176.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>200</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>304</v>
+      </c>
+      <c r="H3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>500</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>304</v>
+      </c>
+      <c r="H4" t="s">
+        <v>299</v>
+      </c>
+      <c r="I4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>304</v>
+      </c>
+      <c r="H5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I5" t="s">
+        <v>311</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>2000</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" t="s">
+        <v>509</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>304</v>
+      </c>
+      <c r="H6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I6" t="s">
+        <v>314</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6">
+        <v>6000</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>304</v>
+      </c>
+      <c r="H7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I7" t="s">
+        <v>317</v>
+      </c>
+      <c r="J7">
+        <v>75</v>
+      </c>
+      <c r="K7">
+        <v>8000</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" t="s">
+        <v>507</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>304</v>
+      </c>
+      <c r="H8" t="s">
+        <v>299</v>
+      </c>
+      <c r="I8" t="s">
+        <v>320</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>12000</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>304</v>
+      </c>
+      <c r="H9" t="s">
+        <v>299</v>
+      </c>
+      <c r="I9" t="s">
+        <v>323</v>
+      </c>
+      <c r="J9">
+        <v>150</v>
+      </c>
+      <c r="K9">
+        <v>15000</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>304</v>
+      </c>
+      <c r="H10" t="s">
+        <v>299</v>
+      </c>
+      <c r="I10" t="s">
+        <v>326</v>
+      </c>
+      <c r="J10">
+        <v>200</v>
+      </c>
+      <c r="K10">
+        <v>20000</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11" t="s">
+        <v>502</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>304</v>
+      </c>
+      <c r="H11" t="s">
+        <v>299</v>
+      </c>
+      <c r="I11" t="s">
+        <v>329</v>
+      </c>
+      <c r="J11">
+        <v>300</v>
+      </c>
+      <c r="K11">
+        <v>30000</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" t="s">
+        <v>511</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H12" t="s">
+        <v>299</v>
+      </c>
+      <c r="I12" t="s">
+        <v>332</v>
+      </c>
+      <c r="J12">
+        <v>500</v>
+      </c>
+      <c r="K12">
+        <v>50000</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" t="s">
+        <v>512</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="s">
+        <v>304</v>
+      </c>
+      <c r="H13" t="s">
+        <v>299</v>
+      </c>
+      <c r="I13" t="s">
+        <v>335</v>
+      </c>
+      <c r="J13">
+        <v>800</v>
+      </c>
+      <c r="K13">
+        <v>80000</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" t="s">
+        <v>337</v>
+      </c>
+      <c r="D14" t="s">
+        <v>492</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>338</v>
+      </c>
+      <c r="H14" t="s">
+        <v>299</v>
+      </c>
+      <c r="I14" t="s">
+        <v>339</v>
+      </c>
+      <c r="M14">
+        <v>20</v>
+      </c>
+      <c r="N14" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>341</v>
+      </c>
+      <c r="B15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" t="s">
+        <v>506</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>338</v>
+      </c>
+      <c r="H15" t="s">
+        <v>299</v>
+      </c>
+      <c r="I15" t="s">
+        <v>343</v>
+      </c>
+      <c r="M15">
+        <v>50</v>
+      </c>
+      <c r="N15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" t="s">
+        <v>513</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" t="s">
+        <v>338</v>
+      </c>
+      <c r="H16" t="s">
+        <v>299</v>
+      </c>
+      <c r="I16" t="s">
+        <v>346</v>
+      </c>
+      <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" t="s">
+        <v>491</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" t="s">
+        <v>338</v>
+      </c>
+      <c r="H17" t="s">
+        <v>299</v>
+      </c>
+      <c r="I17" t="s">
+        <v>349</v>
+      </c>
+      <c r="M17">
+        <v>200</v>
+      </c>
+      <c r="N17" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>350</v>
+      </c>
+      <c r="B18" t="s">
+        <v>351</v>
+      </c>
+      <c r="D18" t="s">
+        <v>499</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>338</v>
+      </c>
+      <c r="H18" t="s">
+        <v>299</v>
+      </c>
+      <c r="I18" t="s">
+        <v>352</v>
+      </c>
+      <c r="M18">
+        <v>300</v>
+      </c>
+      <c r="N18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B19" t="s">
+        <v>354</v>
+      </c>
+      <c r="D19" t="s">
+        <v>505</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>338</v>
+      </c>
+      <c r="H19" t="s">
+        <v>299</v>
+      </c>
+      <c r="I19" t="s">
+        <v>355</v>
+      </c>
+      <c r="M19">
+        <v>500</v>
+      </c>
+      <c r="N19" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>356</v>
+      </c>
+      <c r="B20" t="s">
+        <v>357</v>
+      </c>
+      <c r="D20" t="s">
+        <v>501</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" t="s">
+        <v>338</v>
+      </c>
+      <c r="H20" t="s">
+        <v>299</v>
+      </c>
+      <c r="I20" t="s">
+        <v>358</v>
+      </c>
+      <c r="M20">
+        <v>800</v>
+      </c>
+      <c r="N20" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>359</v>
+      </c>
+      <c r="B21" t="s">
+        <v>360</v>
+      </c>
+      <c r="D21" t="s">
+        <v>498</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" t="s">
+        <v>361</v>
+      </c>
+      <c r="H21" t="s">
+        <v>299</v>
+      </c>
+      <c r="I21" t="s">
+        <v>362</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>364</v>
+      </c>
+      <c r="B22" t="s">
+        <v>365</v>
+      </c>
+      <c r="D22" t="s">
+        <v>489</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
+        <v>361</v>
+      </c>
+      <c r="H22" t="s">
+        <v>299</v>
+      </c>
+      <c r="I22" t="s">
+        <v>366</v>
+      </c>
+      <c r="J22">
+        <v>5</v>
+      </c>
+      <c r="N22" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" t="s">
+        <v>368</v>
+      </c>
+      <c r="D23" t="s">
+        <v>500</v>
+      </c>
+      <c r="E23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="s">
+        <v>361</v>
+      </c>
+      <c r="H23" t="s">
+        <v>299</v>
+      </c>
+      <c r="I23" t="s">
+        <v>369</v>
+      </c>
+      <c r="N23" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>370</v>
+      </c>
+      <c r="B24" t="s">
+        <v>371</v>
+      </c>
+      <c r="D24" t="s">
+        <v>494</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" t="s">
+        <v>372</v>
+      </c>
+      <c r="H24" t="s">
+        <v>373</v>
+      </c>
+      <c r="I24" t="s">
+        <v>374</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
+        <v>25</v>
+      </c>
+      <c r="M24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25" t="s">
+        <v>376</v>
+      </c>
+      <c r="D25" t="s">
+        <v>493</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>372</v>
+      </c>
+      <c r="H25" t="s">
+        <v>373</v>
+      </c>
+      <c r="I25" t="s">
+        <v>377</v>
+      </c>
+      <c r="J25">
+        <v>6</v>
+      </c>
+      <c r="K25">
+        <v>50</v>
+      </c>
+      <c r="M25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>378</v>
+      </c>
+      <c r="B26" t="s">
+        <v>379</v>
+      </c>
+      <c r="D26" t="s">
+        <v>495</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" t="s">
+        <v>372</v>
+      </c>
+      <c r="H26" t="s">
+        <v>373</v>
+      </c>
+      <c r="I26" t="s">
+        <v>380</v>
+      </c>
+      <c r="J26">
+        <v>15</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="M26">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" t="s">
+        <v>496</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" t="s">
+        <v>372</v>
+      </c>
+      <c r="H27" t="s">
+        <v>373</v>
+      </c>
+      <c r="I27" t="s">
+        <v>383</v>
+      </c>
+      <c r="J27">
+        <v>40</v>
+      </c>
+      <c r="K27">
+        <v>300</v>
+      </c>
+      <c r="M27">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>384</v>
+      </c>
+      <c r="B28" t="s">
+        <v>385</v>
+      </c>
+      <c r="D28" t="s">
+        <v>497</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" t="s">
+        <v>372</v>
+      </c>
+      <c r="H28" t="s">
+        <v>373</v>
+      </c>
+      <c r="I28" t="s">
+        <v>386</v>
+      </c>
+      <c r="J28">
+        <v>60</v>
+      </c>
+      <c r="K28">
+        <v>500</v>
+      </c>
+      <c r="M28">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B29" t="s">
+        <v>388</v>
+      </c>
+      <c r="D29" t="s">
+        <v>487</v>
+      </c>
+      <c r="E29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" t="s">
+        <v>389</v>
+      </c>
+      <c r="G29" t="s">
+        <v>298</v>
+      </c>
+      <c r="H29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I29" t="s">
+        <v>390</v>
+      </c>
+      <c r="J29">
+        <v>6</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29">
+        <v>15</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>392</v>
+      </c>
+      <c r="B30" t="s">
+        <v>393</v>
+      </c>
+      <c r="D30" t="s">
+        <v>486</v>
+      </c>
+      <c r="E30" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>304</v>
+      </c>
+      <c r="H30" t="s">
+        <v>299</v>
+      </c>
+      <c r="I30" t="s">
+        <v>394</v>
+      </c>
+      <c r="K30">
+        <v>30000</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30">
+        <v>50</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>396</v>
+      </c>
+      <c r="B31" t="s">
+        <v>397</v>
+      </c>
+      <c r="D31" t="s">
+        <v>514</v>
+      </c>
+      <c r="E31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>304</v>
+      </c>
+      <c r="H31" t="s">
+        <v>299</v>
+      </c>
+      <c r="I31" t="s">
+        <v>398</v>
+      </c>
+      <c r="K31">
+        <v>30000</v>
+      </c>
+      <c r="L31">
+        <v>10</v>
+      </c>
+      <c r="M31">
+        <v>50</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>399</v>
+      </c>
+      <c r="B32" t="s">
+        <v>400</v>
+      </c>
+      <c r="D32" t="s">
+        <v>515</v>
+      </c>
+      <c r="E32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" t="s">
+        <v>304</v>
+      </c>
+      <c r="H32" t="s">
+        <v>299</v>
+      </c>
+      <c r="I32" t="s">
+        <v>401</v>
+      </c>
+      <c r="K32">
+        <v>30000</v>
+      </c>
+      <c r="L32">
+        <v>25</v>
+      </c>
+      <c r="M32">
+        <v>50</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>402</v>
+      </c>
+      <c r="B33" t="s">
+        <v>403</v>
+      </c>
+      <c r="D33" t="s">
+        <v>518</v>
+      </c>
+      <c r="E33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" t="s">
+        <v>304</v>
+      </c>
+      <c r="H33" t="s">
+        <v>299</v>
+      </c>
+      <c r="I33" t="s">
+        <v>404</v>
+      </c>
+      <c r="K33">
+        <v>30000</v>
+      </c>
+      <c r="L33">
+        <v>50</v>
+      </c>
+      <c r="M33">
+        <v>50</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>405</v>
+      </c>
+      <c r="B34" t="s">
+        <v>406</v>
+      </c>
+      <c r="D34" t="s">
+        <v>517</v>
+      </c>
+      <c r="E34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" t="s">
+        <v>304</v>
+      </c>
+      <c r="H34" t="s">
+        <v>299</v>
+      </c>
+      <c r="I34" t="s">
+        <v>407</v>
+      </c>
+      <c r="K34">
+        <v>30000</v>
+      </c>
+      <c r="L34">
+        <v>75</v>
+      </c>
+      <c r="M34">
+        <v>50</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>408</v>
+      </c>
+      <c r="B35" t="s">
+        <v>409</v>
+      </c>
+      <c r="D35" t="s">
+        <v>522</v>
+      </c>
+      <c r="E35" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" t="s">
+        <v>304</v>
+      </c>
+      <c r="H35" t="s">
+        <v>299</v>
+      </c>
+      <c r="I35" t="s">
+        <v>410</v>
+      </c>
+      <c r="K35">
+        <v>30000</v>
+      </c>
+      <c r="L35">
+        <v>100</v>
+      </c>
+      <c r="M35">
+        <v>50</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>411</v>
+      </c>
+      <c r="B36" t="s">
+        <v>412</v>
+      </c>
+      <c r="D36" t="s">
+        <v>519</v>
+      </c>
+      <c r="E36" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" t="s">
+        <v>304</v>
+      </c>
+      <c r="H36" t="s">
+        <v>299</v>
+      </c>
+      <c r="I36" t="s">
+        <v>413</v>
+      </c>
+      <c r="K36">
+        <v>30000</v>
+      </c>
+      <c r="L36">
+        <v>150</v>
+      </c>
+      <c r="M36">
+        <v>50</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>414</v>
+      </c>
+      <c r="B37" t="s">
+        <v>415</v>
+      </c>
+      <c r="D37" t="s">
+        <v>520</v>
+      </c>
+      <c r="E37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" t="s">
+        <v>304</v>
+      </c>
+      <c r="H37" t="s">
+        <v>299</v>
+      </c>
+      <c r="I37" t="s">
+        <v>416</v>
+      </c>
+      <c r="K37">
+        <v>30000</v>
+      </c>
+      <c r="L37">
+        <v>200</v>
+      </c>
+      <c r="M37">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>417</v>
+      </c>
+      <c r="B38" t="s">
+        <v>418</v>
+      </c>
+      <c r="D38" t="s">
+        <v>521</v>
+      </c>
+      <c r="E38" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" t="s">
+        <v>304</v>
+      </c>
+      <c r="H38" t="s">
+        <v>299</v>
+      </c>
+      <c r="I38" t="s">
+        <v>419</v>
+      </c>
+      <c r="K38">
+        <v>30000</v>
+      </c>
+      <c r="L38">
+        <v>250</v>
+      </c>
+      <c r="M38">
+        <v>50</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>420</v>
+      </c>
+      <c r="B39" t="s">
+        <v>421</v>
+      </c>
+      <c r="D39" t="s">
+        <v>516</v>
+      </c>
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" t="s">
+        <v>361</v>
+      </c>
+      <c r="H39" t="s">
+        <v>299</v>
+      </c>
+      <c r="I39" t="s">
+        <v>422</v>
+      </c>
+      <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="N39" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>424</v>
+      </c>
+      <c r="B40" t="s">
+        <v>425</v>
+      </c>
+      <c r="D40" t="s">
+        <v>523</v>
+      </c>
+      <c r="E40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" t="s">
+        <v>304</v>
+      </c>
+      <c r="H40" t="s">
+        <v>299</v>
+      </c>
+      <c r="I40" t="s">
+        <v>426</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
+      <c r="K40">
+        <v>30000</v>
+      </c>
+      <c r="M40">
+        <v>50</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>427</v>
+      </c>
+      <c r="B41" t="s">
+        <v>428</v>
+      </c>
+      <c r="D41" t="s">
+        <v>529</v>
+      </c>
+      <c r="E41" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" t="s">
+        <v>304</v>
+      </c>
+      <c r="H41" t="s">
+        <v>299</v>
+      </c>
+      <c r="I41" t="s">
+        <v>429</v>
+      </c>
+      <c r="J41">
+        <v>10</v>
+      </c>
+      <c r="K41">
+        <v>30000</v>
+      </c>
+      <c r="M41">
+        <v>50</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>430</v>
+      </c>
+      <c r="B42" t="s">
+        <v>431</v>
+      </c>
+      <c r="D42" t="s">
+        <v>524</v>
+      </c>
+      <c r="E42" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" t="s">
+        <v>304</v>
+      </c>
+      <c r="H42" t="s">
+        <v>299</v>
+      </c>
+      <c r="I42" t="s">
+        <v>432</v>
+      </c>
+      <c r="J42">
+        <v>25</v>
+      </c>
+      <c r="K42">
+        <v>30000</v>
+      </c>
+      <c r="M42">
+        <v>50</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>433</v>
+      </c>
+      <c r="B43" t="s">
+        <v>434</v>
+      </c>
+      <c r="D43" t="s">
+        <v>528</v>
+      </c>
+      <c r="E43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F43" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" t="s">
+        <v>304</v>
+      </c>
+      <c r="H43" t="s">
+        <v>299</v>
+      </c>
+      <c r="I43" t="s">
+        <v>435</v>
+      </c>
+      <c r="J43">
+        <v>50</v>
+      </c>
+      <c r="K43">
+        <v>30000</v>
+      </c>
+      <c r="M43">
+        <v>50</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>436</v>
+      </c>
+      <c r="B44" t="s">
+        <v>437</v>
+      </c>
+      <c r="D44" t="s">
+        <v>526</v>
+      </c>
+      <c r="E44" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" t="s">
+        <v>304</v>
+      </c>
+      <c r="H44" t="s">
+        <v>299</v>
+      </c>
+      <c r="I44" t="s">
+        <v>438</v>
+      </c>
+      <c r="J44">
+        <v>75</v>
+      </c>
+      <c r="K44">
+        <v>30000</v>
+      </c>
+      <c r="M44">
+        <v>50</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>439</v>
+      </c>
+      <c r="B45" t="s">
+        <v>440</v>
+      </c>
+      <c r="D45" t="s">
+        <v>525</v>
+      </c>
+      <c r="E45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" t="s">
+        <v>304</v>
+      </c>
+      <c r="H45" t="s">
+        <v>299</v>
+      </c>
+      <c r="I45" t="s">
+        <v>441</v>
+      </c>
+      <c r="J45">
+        <v>100</v>
+      </c>
+      <c r="K45">
+        <v>30000</v>
+      </c>
+      <c r="M45">
+        <v>50</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>442</v>
+      </c>
+      <c r="B46" t="s">
+        <v>443</v>
+      </c>
+      <c r="D46" t="s">
+        <v>527</v>
+      </c>
+      <c r="E46" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" t="s">
+        <v>43</v>
+      </c>
+      <c r="G46" t="s">
+        <v>361</v>
+      </c>
+      <c r="H46" t="s">
+        <v>299</v>
+      </c>
+      <c r="I46" t="s">
+        <v>444</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="N46" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>446</v>
+      </c>
+      <c r="C47" t="s">
+        <v>531</v>
+      </c>
+      <c r="E47" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" t="s">
+        <v>389</v>
+      </c>
+      <c r="G47" t="s">
+        <v>298</v>
+      </c>
+      <c r="H47" t="s">
+        <v>298</v>
+      </c>
+      <c r="I47" t="s">
+        <v>447</v>
+      </c>
+      <c r="M47" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>448</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA03F59A-0EC6-450E-AE18-243FFD97199D}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="107.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="111.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC46E614-3935-4A35-AF14-2BF587B575D4}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="10"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>479</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{599491C1-ECFA-4332-92BD-67AB5ED41907}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
